--- a/Un_poco_de_historia_11.xlsx
+++ b/Un_poco_de_historia_11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Historia informática\Web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6655EE3-8C5C-40A5-A997-E41F3F9BFD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7831D4B0-3218-4D73-A659-FDC116794351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="5100" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="586">
   <si>
     <t xml:space="preserve">Año </t>
   </si>
@@ -143,16 +143,10 @@
     <t>Manual, caja o fotos del equipo, si se conservan.</t>
   </si>
   <si>
-    <t>Nace la revista PC Magazine Actual (1988); en 1991 pasa a llamarse PC Actual.</t>
-  </si>
-  <si>
     <t>Compre el primer número de PC Magazin Actual. PCActual en 1991. Lo compré ininterrumpidamente hasta el Nº 140 (aúnque solo conservo las revistas nº 99 y nº 107 de PCActual, porque me publicaron sendos programas en ella, sí que conservo todos los CD)</t>
   </si>
   <si>
     <t>Resuelto con tu repositorio: nº 99 = julio/agosto de 1998 (CD nº 25, pág. 321) y nº 107 = abril de 1999 (CD nº 33, pág. 353). Mi alerta anterior partía de 12 números al año y era errónea: con unos 10-11 al año (hay dobles, como el de jul/ago), el nº 107 de abril de 1999 cuadra con un nº 1 hacia 1988-89, sin necesidad de renumeración. Lo confirmaría el nº 1 o cualquier número fechado.</t>
-  </si>
-  <si>
-    <t>Zontrox01/MisProgramasRetro: Algunos de mis programas hechos en el milenio pasado. | Portadas de los nº 99 y 107 de PC Actual y los CD (prueba directa de las publicaciones).</t>
   </si>
   <si>
     <t>Compré el Amstrad 1640</t>
@@ -1685,9 +1679,6 @@
     <t>Cumplo 1 año.</t>
   </si>
   <si>
-    <t>Cumplo 2 años.</t>
-  </si>
-  <si>
     <t>Cumplo 3 años.</t>
   </si>
   <si>
@@ -1704,9 +1695,6 @@
   </si>
   <si>
     <t>Cumplo 8 años.</t>
-  </si>
-  <si>
-    <t>Cumplo 9 años.</t>
   </si>
   <si>
     <t xml:space="preserve">El 11 de septiembre me casé con Juani. </t>
@@ -1888,7 +1876,36 @@
 Fábrica: varios proyectos unificados en una web con Drupal 11.2.3 (seguridad, Top10, Top60, control de LOTO, permisos de trabajo, registro Knowledge). El registro de personal con tarjetas RFID fue desestimado.</t>
   </si>
   <si>
-    <t>Ví la HP-41. El Sr. Rizo trajo a clase de tecnología química, su nueva adquisición. Una flamante Calculadora programable</t>
+    <t>Ví la HP-41CV. El Sr. Rizo trajo a clase de tecnología química, su nueva adquisición. Una flamante Calculadora programable</t>
+  </si>
+  <si>
+    <t>Cumplo 2 años. Nace mi hermano Santi</t>
+  </si>
+  <si>
+    <t>Cumplo 9 años. Nace mi hermana Begoña</t>
+  </si>
+  <si>
+    <t>Nace mi hermano Moisés</t>
+  </si>
+  <si>
+    <t>Nace la revista PC Magazine Actual (1988); en 1991 pasa a llamarse PC Actual. 
+Se crea el dominio .es</t>
+  </si>
+  <si>
+    <t>Se crea el dominio .cat</t>
+  </si>
+  <si>
+    <t>Se abre al público el dominio .cat</t>
+  </si>
+  <si>
+    <t>https://es.wikipedia.org/wiki/.cat</t>
+  </si>
+  <si>
+    <t>Zontrox01/MisProgramasRetro: Algunos de mis programas hechos en el milenio pasado. | Portadas de los nº 99 y 107 de PC Actual y los CD (prueba directa de las publicaciones).
+https://es.wikipedia.org/wiki/.es</t>
+  </si>
+  <si>
+    <t>https://zontrox01.github.io/Un-poco-de-historia/</t>
   </si>
 </sst>
 </file>
@@ -1971,7 +1988,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2001,6 +2018,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2339,13 +2357,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>2</v>
@@ -2354,7 +2372,7 @@
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -2375,7 +2393,7 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -2393,7 +2411,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -2411,7 +2429,7 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>534</v>
+        <v>577</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -2429,7 +2447,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -2447,11 +2465,11 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -2467,7 +2485,7 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -2487,11 +2505,11 @@
         <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -2511,7 +2529,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -2531,7 +2549,7 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -2549,7 +2567,7 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -2600,7 +2618,9 @@
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>579</v>
+      </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -2618,7 +2638,9 @@
         <v>1978</v>
       </c>
       <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="C15" s="11" t="s">
+        <v>585</v>
+      </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -2639,7 +2661,7 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -2660,13 +2682,13 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -2688,10 +2710,10 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -2712,10 +2734,10 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -2736,10 +2758,10 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -2762,10 +2784,10 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -2786,10 +2808,10 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>23</v>
@@ -2870,17 +2892,17 @@
         <v>1988</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>580</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -2888,10 +2910,10 @@
         <v>19</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>40</v>
+        <v>584</v>
       </c>
       <c r="L25" s="2"/>
     </row>
@@ -2905,7 +2927,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>34</v>
@@ -2913,7 +2935,7 @@
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>36</v>
@@ -2925,10 +2947,10 @@
         <v>1990</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>28</v>
@@ -2949,35 +2971,35 @@
         <v>1991</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L28" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="75" x14ac:dyDescent="0.25">
@@ -2985,29 +3007,29 @@
         <v>1992</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L29" s="2"/>
     </row>
@@ -3016,29 +3038,29 @@
         <v>1993</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
@@ -3048,31 +3070,31 @@
         <v>1994</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L31" s="2"/>
     </row>
@@ -3081,31 +3103,31 @@
         <v>1995</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L32" s="2"/>
     </row>
@@ -3118,21 +3140,21 @@
         <v>28</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L33" s="2"/>
     </row>
@@ -3146,11 +3168,11 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
@@ -3162,32 +3184,32 @@
         <v>1998</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J35" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L35" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -3195,34 +3217,34 @@
         <v>1999</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" t="s">
+        <v>567</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C36" t="s">
-        <v>571</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="F36" s="2" t="s">
+      <c r="H36" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3230,31 +3252,31 @@
         <v>2000</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="F37" s="2" t="s">
+      <c r="H37" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J37" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="L37" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3262,25 +3284,25 @@
         <v>2001</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L38" s="2"/>
     </row>
@@ -3290,27 +3312,27 @@
       </c>
       <c r="B39" s="2"/>
       <c r="D39" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="I39" s="2"/>
       <c r="J39" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L39" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="60" x14ac:dyDescent="0.25">
@@ -3319,17 +3341,17 @@
       </c>
       <c r="B40" s="2"/>
       <c r="D40" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
@@ -3340,17 +3362,17 @@
       </c>
       <c r="B41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
@@ -3359,9 +3381,11 @@
       <c r="A42" s="2">
         <v>2005</v>
       </c>
-      <c r="B42" s="6"/>
+      <c r="B42" s="6" t="s">
+        <v>581</v>
+      </c>
       <c r="D42" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -3370,15 +3394,19 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
+      <c r="L42" s="11" t="s">
+        <v>583</v>
+      </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>2006</v>
       </c>
-      <c r="B43" s="6"/>
+      <c r="B43" s="6" t="s">
+        <v>582</v>
+      </c>
       <c r="D43" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -3394,20 +3422,20 @@
         <v>2007</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>10</v>
@@ -3422,20 +3450,20 @@
       </c>
       <c r="B45" s="6"/>
       <c r="D45" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L45" s="2"/>
     </row>
@@ -3444,25 +3472,25 @@
         <v>2009</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L46" s="2"/>
     </row>
@@ -3471,26 +3499,26 @@
         <v>2010</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="F47" s="2" t="s">
+      <c r="H47" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L47" s="2"/>
     </row>
@@ -3499,14 +3527,14 @@
         <v>2011</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
@@ -3519,20 +3547,20 @@
         <v>2012</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L49" s="2"/>
     </row>
@@ -3541,17 +3569,17 @@
         <v>2013</v>
       </c>
       <c r="C50" t="s">
+        <v>565</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>573</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
@@ -3564,14 +3592,14 @@
         <v>2014</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
@@ -3584,14 +3612,14 @@
         <v>2015</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
@@ -3605,17 +3633,17 @@
       </c>
       <c r="B53" s="6"/>
       <c r="D53" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
@@ -3626,10 +3654,10 @@
       </c>
       <c r="B54" s="2"/>
       <c r="D54" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -3645,10 +3673,10 @@
       </c>
       <c r="B55" s="2"/>
       <c r="D55" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -3664,10 +3692,10 @@
       </c>
       <c r="B56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -3683,29 +3711,29 @@
       </c>
       <c r="B57" s="2"/>
       <c r="D57" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="F57" s="2" t="s">
+      <c r="H57" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="I57" s="2"/>
       <c r="J57" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="L57" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="L57" s="2" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3713,10 +3741,10 @@
         <v>2021</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
@@ -3735,7 +3763,7 @@
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
@@ -3745,10 +3773,10 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3757,7 +3785,7 @@
       </c>
       <c r="B60" s="2"/>
       <c r="C60" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
@@ -3767,7 +3795,7 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L60" s="2"/>
     </row>
@@ -3777,19 +3805,19 @@
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L61" s="2"/>
     </row>
@@ -3799,25 +3827,25 @@
       </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I62" s="2"/>
       <c r="J62" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L62" s="2"/>
     </row>
@@ -3827,19 +3855,19 @@
       </c>
       <c r="B63" s="2"/>
       <c r="C63" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="L63" s="2"/>
     </row>
@@ -3850,6 +3878,8 @@
   <autoFilter ref="A1:J1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="J25" r:id="rId1" display="https://github.com/Zontrox01/MisProgramasRetro" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L42" r:id="rId2" xr:uid="{6C3953BB-1E74-44D0-A26B-9035DC37042A}"/>
+    <hyperlink ref="C15" r:id="rId3" xr:uid="{8462C7D6-25A3-4777-AAD0-77B8C1E23EF6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3873,66 +3903,66 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -3941,16 +3971,16 @@
     </row>
     <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -3959,13 +3989,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -3975,16 +4005,16 @@
     </row>
     <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -3993,34 +4023,34 @@
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -4028,166 +4058,166 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -4195,82 +4225,82 @@
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="E16" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>226</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>230</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
@@ -4279,19 +4309,19 @@
     </row>
     <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -4299,61 +4329,61 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -4375,82 +4405,82 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4458,7 +4488,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4466,31 +4496,31 @@
         <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -4517,277 +4547,277 @@
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>314</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>322</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>326</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>322</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="E10" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -4795,143 +4825,143 @@
     </row>
     <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>350</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="E13" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>360</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>364</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -4939,37 +4969,37 @@
     </row>
     <row r="16" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="G16" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="J16" s="2"/>
     </row>
     <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -5000,138 +5030,138 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>386</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>390</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>394</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>398</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -5151,277 +5181,277 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -5444,260 +5474,260 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>474</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>485</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>490</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>500</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="E9" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>520</v>
       </c>
     </row>
   </sheetData>
